--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Commodities ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Commodities ETF.xlsx
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty Commodities ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -79,6 +79,15 @@
     <t>Power</t>
   </si>
   <si>
+    <t>Tata Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE081A01020</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
     <t>Ultratech Cement Ltd.</t>
   </si>
   <si>
@@ -88,13 +97,16 @@
     <t>Cement &amp; Cement Products</t>
   </si>
   <si>
-    <t>Tata Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE081A01020</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
+    <t>Grasim Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE047A01021</t>
+  </si>
+  <si>
+    <t>JSW Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE019A01038</t>
   </si>
   <si>
     <t>Oil &amp; Natural Gas Corporation Ltd.</t>
@@ -106,16 +118,13 @@
     <t>Oil</t>
   </si>
   <si>
-    <t>Grasim Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE047A01021</t>
-  </si>
-  <si>
-    <t>JSW Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE019A01038</t>
+    <t>Hindalco Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE038A01020</t>
+  </si>
+  <si>
+    <t>Non - Ferrous Metals</t>
   </si>
   <si>
     <t>Coal India Ltd.</t>
@@ -127,15 +136,6 @@
     <t>Consumable Fuels</t>
   </si>
   <si>
-    <t>Hindalco Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE038A01020</t>
-  </si>
-  <si>
-    <t>Non - Ferrous Metals</t>
-  </si>
-  <si>
     <t>Vedanta Ltd.</t>
   </si>
   <si>
@@ -172,34 +172,64 @@
     <t>Chemicals &amp; Petrochemicals</t>
   </si>
   <si>
+    <t>Adani Power Ltd.</t>
+  </si>
+  <si>
+    <t>INE814H01011</t>
+  </si>
+  <si>
     <t>SRF Ltd.</t>
   </si>
   <si>
     <t>INE647A01010</t>
   </si>
   <si>
-    <t>Adani Power Ltd.</t>
-  </si>
-  <si>
-    <t>INE814H01011</t>
-  </si>
-  <si>
     <t>Shree Cements Ltd.</t>
   </si>
   <si>
     <t>INE070A01015</t>
   </si>
   <si>
+    <t>Hindustan Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE094A01015</t>
+  </si>
+  <si>
     <t>Ambuja Cements Ltd.</t>
   </si>
   <si>
     <t>INE079A01024</t>
   </si>
   <si>
-    <t>Hindustan Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE094A01015</t>
+    <t>Jindal Steel &amp; Power Ltd.</t>
+  </si>
+  <si>
+    <t>INE749A01030</t>
+  </si>
+  <si>
+    <t>APL Apollo Tubes Ltd.</t>
+  </si>
+  <si>
+    <t>INE702C01027</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>UPL Ltd.</t>
+  </si>
+  <si>
+    <t>INE628A01036</t>
+  </si>
+  <si>
+    <t>Fertilizers &amp; Agrochemicals</t>
+  </si>
+  <si>
+    <t>Adani Energy Solutions Ltd.</t>
+  </si>
+  <si>
+    <t>INE931S01010</t>
   </si>
   <si>
     <t>Adani Green Energy Ltd.</t>
@@ -208,34 +238,22 @@
     <t>INE364U01010</t>
   </si>
   <si>
-    <t>UPL Ltd.</t>
-  </si>
-  <si>
-    <t>INE628A01036</t>
-  </si>
-  <si>
-    <t>Fertilizers &amp; Agrochemicals</t>
-  </si>
-  <si>
-    <t>Jindal Steel &amp; Power Ltd.</t>
-  </si>
-  <si>
-    <t>INE749A01030</t>
-  </si>
-  <si>
     <t>PI Industries Ltd.</t>
   </si>
   <si>
     <t>INE603J01030</t>
   </si>
   <si>
-    <t>APL Apollo Tubes Ltd.</t>
-  </si>
-  <si>
-    <t>INE702C01027</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
+    <t>NHPC Ltd.</t>
+  </si>
+  <si>
+    <t>INE848E01016</t>
+  </si>
+  <si>
+    <t>Torrent Power Ltd.</t>
+  </si>
+  <si>
+    <t>INE813H01021</t>
   </si>
   <si>
     <t>JSW Energy Ltd</t>
@@ -244,18 +262,6 @@
     <t>INE121E01018</t>
   </si>
   <si>
-    <t>Adani Energy Solutions Ltd.</t>
-  </si>
-  <si>
-    <t>INE931S01010</t>
-  </si>
-  <si>
-    <t>NHPC Ltd.</t>
-  </si>
-  <si>
-    <t>INE848E01016</t>
-  </si>
-  <si>
     <t>NMDC Ltd.</t>
   </si>
   <si>
@@ -265,16 +271,10 @@
     <t>Minerals &amp; Mining</t>
   </si>
   <si>
-    <t>Steel Authority Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE114A01011</t>
-  </si>
-  <si>
-    <t>ACC Ltd.</t>
-  </si>
-  <si>
-    <t>INE012A01025</t>
+    <t>Oil India Ltd.</t>
+  </si>
+  <si>
+    <t>INE274J01014</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -334,7 +334,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -1214,10 +1214,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>7181.659999999999</v>
+        <v>7204.58</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9985987229582999</v>
+        <v>0.9999557800561001</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1251,10 +1251,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>7181.659999999999</v>
+        <v>7204.58</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9985987229582999</v>
+        <v>0.9999557800561001</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1277,13 +1277,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>59979</v>
+        <v>55365</v>
       </c>
       <c r="G8" s="15">
-        <v>758.79</v>
+        <v>786.68</v>
       </c>
       <c r="H8" s="16">
-        <v>0.1055085767071</v>
+        <v>0.1091868246387</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1306,13 +1306,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>189790</v>
+        <v>177624</v>
       </c>
       <c r="G9" s="15">
-        <v>614.92</v>
+        <v>593.09</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0855036755739</v>
+        <v>0.0823176054113</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1335,13 +1335,13 @@
         <v>23</v>
       </c>
       <c r="F10" s="14">
-        <v>4571</v>
+        <v>309760</v>
       </c>
       <c r="G10" s="15">
-        <v>525.09</v>
+        <v>498.78</v>
       </c>
       <c r="H10" s="16">
-        <v>0.073012952916</v>
+        <v>0.069227900027</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1364,13 +1364,13 @@
         <v>26</v>
       </c>
       <c r="F11" s="14">
-        <v>332125</v>
+        <v>4358</v>
       </c>
       <c r="G11" s="15">
-        <v>447.11</v>
+        <v>488.53</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0621699544426</v>
+        <v>0.0678052568271</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1390,16 +1390,16 @@
         <v>13</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F12" s="14">
-        <v>155468</v>
+        <v>14378</v>
       </c>
       <c r="G12" s="15">
-        <v>408.27</v>
+        <v>366.04</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0567693124741</v>
+        <v>0.0508043236014</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1410,10 +1410,10 @@
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1">
       <c r="B13" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>30</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>31</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>13</v>
@@ -1422,13 +1422,13 @@
         <v>23</v>
       </c>
       <c r="F13" s="14">
-        <v>14893</v>
+        <v>35541</v>
       </c>
       <c r="G13" s="15">
-        <v>373.64</v>
+        <v>353.10</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0519540644985</v>
+        <v>0.049008323308</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1439,25 +1439,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>26</v>
-      </c>
       <c r="F14" s="14">
-        <v>38464</v>
+        <v>145502</v>
       </c>
       <c r="G14" s="15">
-        <v>363.48</v>
+        <v>348.33</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0505413322019</v>
+        <v>0.0483462737408</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1480,13 +1480,13 @@
         <v>36</v>
       </c>
       <c r="F15" s="14">
-        <v>90910</v>
+        <v>54235</v>
       </c>
       <c r="G15" s="15">
-        <v>359.91</v>
+        <v>343.58</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0500449292197</v>
+        <v>0.0476870000627</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1509,13 +1509,13 @@
         <v>39</v>
       </c>
       <c r="F16" s="14">
-        <v>58265</v>
+        <v>85085</v>
       </c>
       <c r="G16" s="15">
-        <v>346.27</v>
+        <v>338.04</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0481483083018</v>
+        <v>0.0469180787624</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1538,13 +1538,13 @@
         <v>42</v>
       </c>
       <c r="F17" s="14">
-        <v>67944</v>
+        <v>63564</v>
       </c>
       <c r="G17" s="15">
-        <v>299.9</v>
+        <v>276.85</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0417006314717</v>
+        <v>0.0384252458448</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1567,13 +1567,13 @@
         <v>20</v>
       </c>
       <c r="F18" s="14">
-        <v>67658</v>
+        <v>62899</v>
       </c>
       <c r="G18" s="15">
-        <v>246.61</v>
+        <v>247.07</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0342907393373</v>
+        <v>0.0342919468697</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1596,13 +1596,13 @@
         <v>17</v>
       </c>
       <c r="F19" s="14">
-        <v>77576</v>
+        <v>72605</v>
       </c>
       <c r="G19" s="15">
-        <v>202.55</v>
+        <v>231.17</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0281642644368</v>
+        <v>0.032085114979</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1625,13 +1625,13 @@
         <v>17</v>
       </c>
       <c r="F20" s="14">
-        <v>150149</v>
+        <v>139967</v>
       </c>
       <c r="G20" s="15">
-        <v>192.93</v>
+        <v>198.71</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0268266183056</v>
+        <v>0.027579846855</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1654,13 +1654,13 @@
         <v>51</v>
       </c>
       <c r="F21" s="14">
-        <v>6161</v>
+        <v>5766</v>
       </c>
       <c r="G21" s="15">
-        <v>176.93</v>
+        <v>179.16</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0246018430353</v>
+        <v>0.0248664151907</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1680,16 +1680,16 @@
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F22" s="14">
-        <v>5810</v>
+        <v>29485</v>
       </c>
       <c r="G22" s="15">
-        <v>163.25</v>
+        <v>160.34</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0226996601792</v>
+        <v>0.0222543034811</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1709,16 +1709,16 @@
         <v>13</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F23" s="14">
-        <v>31504</v>
+        <v>5435</v>
       </c>
       <c r="G23" s="15">
-        <v>161.68</v>
+        <v>155.50</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0224813541058</v>
+        <v>0.0215825383018</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1738,16 +1738,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F24" s="14">
-        <v>538</v>
+        <v>500</v>
       </c>
       <c r="G24" s="15">
-        <v>149.54</v>
+        <v>147.98</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0207933058695</v>
+        <v>0.0205388039737</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1767,16 +1767,16 @@
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F25" s="14">
-        <v>26895</v>
+        <v>35982</v>
       </c>
       <c r="G25" s="15">
-        <v>137.92</v>
+        <v>147.90</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0191775628295</v>
+        <v>0.020527700417</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1796,16 +1796,16 @@
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F26" s="14">
-        <v>38448</v>
+        <v>24953</v>
       </c>
       <c r="G26" s="15">
-        <v>137.74</v>
+        <v>138.11</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0191525341077</v>
+        <v>0.0191689026679</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -1825,16 +1825,16 @@
         <v>13</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F27" s="14">
-        <v>12268</v>
+        <v>14232</v>
       </c>
       <c r="G27" s="15">
-        <v>122.38</v>
+        <v>135.05</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0170167498483</v>
+        <v>0.0187441916248</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -1857,13 +1857,13 @@
         <v>66</v>
       </c>
       <c r="F28" s="14">
-        <v>20254</v>
+        <v>6785</v>
       </c>
       <c r="G28" s="15">
-        <v>122.28</v>
+        <v>122.92</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0170028450029</v>
+        <v>0.0170606148428</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -1883,16 +1883,16 @@
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="F29" s="14">
-        <v>15207</v>
+        <v>18957</v>
       </c>
       <c r="G29" s="15">
-        <v>120.37</v>
+        <v>119.03</v>
       </c>
       <c r="H29" s="16">
-        <v>0.016737262455</v>
+        <v>0.0165207043991</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -1903,25 +1903,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="F30" s="14">
-        <v>3250</v>
+        <v>13558</v>
       </c>
       <c r="G30" s="15">
-        <v>113.22</v>
+        <v>117.57</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0157430660061</v>
+        <v>0.0163180644897</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -1932,25 +1932,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="F31" s="14">
-        <v>7247</v>
+        <v>11483</v>
       </c>
       <c r="G31" s="15">
-        <v>109.40</v>
+        <v>116.48</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0152119009103</v>
+        <v>0.0161667785299</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -1970,16 +1970,16 @@
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="F32" s="14">
-        <v>21387</v>
+        <v>3034</v>
       </c>
       <c r="G32" s="15">
-        <v>108.77</v>
+        <v>116.01</v>
       </c>
       <c r="H32" s="16">
-        <v>0.015124300384</v>
+        <v>0.0161015451344</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2002,13 +2002,13 @@
         <v>20</v>
       </c>
       <c r="F33" s="14">
-        <v>14487</v>
+        <v>118527</v>
       </c>
       <c r="G33" s="15">
-        <v>108.41</v>
+        <v>103.60</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0150742429405</v>
+        <v>0.014379105904</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2031,13 +2031,13 @@
         <v>20</v>
       </c>
       <c r="F34" s="14">
-        <v>126662</v>
+        <v>7127</v>
       </c>
       <c r="G34" s="15">
-        <v>102.03</v>
+        <v>97.92</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0141871138014</v>
+        <v>0.0135907533795</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2057,16 +2057,16 @@
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="F35" s="14">
-        <v>138329</v>
+        <v>20021</v>
       </c>
       <c r="G35" s="15">
-        <v>91.44</v>
+        <v>97.69</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0127145906694</v>
+        <v>0.013558830654</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2077,25 +2077,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="D36" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>26</v>
-      </c>
       <c r="F36" s="14">
-        <v>57857</v>
+        <v>129476</v>
       </c>
       <c r="G36" s="15">
-        <v>62.16</v>
+        <v>92.15</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0086432519249</v>
+        <v>0.0127899093538</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2115,16 +2115,16 @@
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F37" s="14">
-        <v>2723</v>
+        <v>20431</v>
       </c>
       <c r="G37" s="15">
-        <v>54.67</v>
+        <v>87.20</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0076017790015</v>
+        <v>0.012102876784</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2639,10 +2639,10 @@
         <v>13</v>
       </c>
       <c r="G65" s="9">
-        <v>5.12</v>
+        <v>5.23</v>
       </c>
       <c r="H65" s="10">
-        <v>0.0007119280864</v>
+        <v>0.0007258950181</v>
       </c>
       <c r="I65" s="9" t="s">
         <v>13</v>
@@ -2676,10 +2676,10 @@
         <v>13</v>
       </c>
       <c r="G67" s="18">
-        <v>4.957616800001233</v>
+        <v>-4.911399799997525</v>
       </c>
       <c r="H67" s="19">
-        <v>0.0006893489535018867</v>
+        <v>-0.0006816750758797896</v>
       </c>
       <c r="I67" s="18" t="s">
         <v>13</v>
@@ -2705,10 +2705,10 @@
         <v>13</v>
       </c>
       <c r="G68" s="18">
-        <v>7191.7376168</v>
+        <v>7204.8986002</v>
       </c>
       <c r="H68" s="19">
-        <v>0.9999999999982019</v>
+        <v>0.9999999999983202</v>
       </c>
       <c r="I68" s="18" t="s">
         <v>13</v>
